--- a/docs/specs/snaphere-api-spec-v1.1.5.xlsx
+++ b/docs/specs/snaphere-api-spec-v1.1.5.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 개요" sheetId="1" r:id="R1e7cb40ec2a44c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. API 목록" sheetId="2" r:id="R036a78b35ba64935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 요청 파라미터" sheetId="3" r:id="R5a17f8a8b357424a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 응답 스키마" sheetId="4" r:id="Ra51b022547ff4829"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 공통 규약" sheetId="5" r:id="Rab8cd1a3222b4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 에러 코드" sheetId="6" r:id="Ra3a4bbe2ec16430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 배치·비동기" sheetId="7" r:id="R2b607c2f75db42e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 요구사항 추적" sheetId="8" r:id="Rec9bee3de8f540d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. ERD 엔터티" sheetId="9" r:id="Rfd8790ab57d04221"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. ERD 관계" sheetId="10" r:id="R2635dbde8a544d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 개요" sheetId="1" r:id="R12d827777b0e44fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. API 목록" sheetId="2" r:id="R96b920b6f27c4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 요청 파라미터" sheetId="3" r:id="Rd711201cf950424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 응답 스키마" sheetId="4" r:id="Rf093336020bc45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 공통 규약" sheetId="5" r:id="Re7bbe8a0e5454d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 에러 코드" sheetId="6" r:id="R039f7824e0284737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 배치·비동기" sheetId="7" r:id="R0e2491da54264f9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 요구사항 추적" sheetId="8" r:id="R7a59adfc22c047f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. ERD 엔터티" sheetId="9" r:id="Rca2e6fc396dc499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. ERD 관계" sheetId="10" r:id="R2e2ffc762c1d438f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1308,7 +1308,7 @@
       </x:c>
       <x:c r="B30" s="48" t="n">
         <x:f>COUNTA('8. ERD 엔터티'!$B$5:$B$80)</x:f>
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="37" t="str"/>
       <x:c r="D30" s="37" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </x:c>
       <x:c r="B31" s="48" t="n">
         <x:f>COUNTA('9. ERD 관계'!$A$5:$A$100)</x:f>
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C31" s="37" t="str"/>
       <x:c r="D31" s="37" t="inlineStr">
@@ -1638,10 +1638,8 @@
           <x:t xml:space="preserve">ERD 산식</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">원본 29개 테이블과 1:1 대응으로 정정(sigungu 분리 · post_rankings 추가)</x:t>
-        </x:is>
+      <x:c r="C47" s="40" t="str">
+        <x:v>사용자 제공 ERD의 실제 28개 테이블과 1:1 대응으로 정정(sigungu 분리 · post_rankings 포함 · tier_logs 제외)</x:v>
       </x:c>
       <x:c r="D47" s="40" t="inlineStr">
         <x:is>
@@ -1682,10 +1680,8 @@
           <x:t xml:space="preserve">누락 14건</x:t>
         </x:is>
       </x:c>
-      <x:c r="C49" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DeletionPreview.imageCount · places.view_count · tier_logs 임계값 · 알림 90일 · SearchResult.matchedRegion · 404 코드 3종 · presign 형식 제약 · 장소명 태그 서버 주입 · sigungu 테이블 등</x:t>
-        </x:is>
+      <x:c r="C49" s="40" t="str">
+        <x:v>DeletionPreview.imageCount · places.view_count · 알림 90일 · SearchResult.matchedRegion · 404 코드 3종 · presign 형식 제약 · 장소명 태그 서버 주입 · sigungu 테이블 등</x:v>
       </x:c>
       <x:c r="D49" s="40" t="inlineStr">
         <x:is>
@@ -1777,10 +1773,8 @@
           <x:t xml:space="preserve">대리키 PK 환원</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs(tier_log_id) · heatmap_cells(cell_id) · place_rankings(ranking_id) · account_deletion_logs(log_id) · search_logs(log_id) — UNIQUE는 별도 제약으로</x:t>
-        </x:is>
+      <x:c r="C55" s="40" t="str">
+        <x:v>heatmap_cells(cell_id) · place_rankings(ranking_id) · account_deletion_logs(log_id) · search_logs(log_id) — UNIQUE는 별도 제약으로</x:v>
       </x:c>
       <x:c r="D55" s="40" t="inlineStr">
         <x:is>
@@ -1992,2104 +1986,1192 @@
       </x:c>
     </x:row>
     <x:row r="4" s="33" customFormat="1" ht="26.399999618530273" customHeight="1">
-      <x:c r="A4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">부모</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">자식</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">관계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FK·참조</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">삭제 정책</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">제약 유형</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설명</x:t>
-        </x:is>
+      <x:c r="A4" s="32" t="str">
+        <x:v>REL ID</x:v>
+      </x:c>
+      <x:c r="B4" s="32" t="str">
+        <x:v>부모</x:v>
+      </x:c>
+      <x:c r="C4" s="32" t="str">
+        <x:v>자식</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="str">
+        <x:v>관계</x:v>
+      </x:c>
+      <x:c r="E4" s="32" t="str">
+        <x:v>FK·참조</x:v>
+      </x:c>
+      <x:c r="F4" s="32" t="str">
+        <x:v>삭제 정책</x:v>
+      </x:c>
+      <x:c r="G4" s="32" t="str">
+        <x:v>제약 유형</x:v>
+      </x:c>
+      <x:c r="H4" s="32" t="str">
+        <x:v>설명</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_devices</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_devices.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">회원 탈퇴 시 기기 제거</x:t>
-        </x:is>
+      <x:c r="A5" s="40" t="str">
+        <x:v>REL-001</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>user_devices</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>user_devices.user_id</x:v>
+      </x:c>
+      <x:c r="F5" s="40" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="str">
+        <x:v>기기 소유자</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-002</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refresh_tokens</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refresh_tokens.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">전체 로그아웃 시 일괄 revoke</x:t>
-        </x:is>
+      <x:c r="A6" s="37" t="str">
+        <x:v>REL-002</x:v>
+      </x:c>
+      <x:c r="B6" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C6" s="37" t="str">
+        <x:v>refresh_tokens</x:v>
+      </x:c>
+      <x:c r="D6" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E6" s="37" t="str">
+        <x:v>refresh_tokens.user_id</x:v>
+      </x:c>
+      <x:c r="F6" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G6" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H6" s="37" t="str">
+        <x:v>토큰 소유자</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-003</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_devices</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refresh_tokens</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refresh_tokens.device_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기기별 세션</x:t>
-        </x:is>
+      <x:c r="A7" s="37" t="str">
+        <x:v>REL-003</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>user_devices</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>refresh_tokens</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>refresh_tokens.device_id</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>기기 세션</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-004</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">account_deletion_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">account_deletion_logs.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT/익명화</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">감사 기록 보존 정책 확인</x:t>
-        </x:is>
+      <x:c r="A8" s="37" t="str">
+        <x:v>REL-004</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="str">
+        <x:v>account_deletion_logs</x:v>
+      </x:c>
+      <x:c r="D8" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E8" s="37" t="str">
+        <x:v>account_deletion_logs.user_id</x:v>
+      </x:c>
+      <x:c r="F8" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G8" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H8" s="37" t="str">
+        <x:v>탈퇴 감사</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follows</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follows.follower_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">팔로우 주체</x:t>
-        </x:is>
+      <x:c r="A9" s="37" t="str">
+        <x:v>REL-005</x:v>
+      </x:c>
+      <x:c r="B9" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>follows</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>follows.follower_id</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>팔로우 주체</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-006</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follows</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follows.following_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">팔로우 대상</x:t>
-        </x:is>
+      <x:c r="A10" s="37" t="str">
+        <x:v>REL-006</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C10" s="37" t="str">
+        <x:v>follows</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="str">
+        <x:v>follows.following_id</x:v>
+      </x:c>
+      <x:c r="F10" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G10" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H10" s="37" t="str">
+        <x:v>팔로우 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-007</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">행정구역</x:t>
-        </x:is>
+      <x:c r="A11" s="37" t="str">
+        <x:v>REL-007</x:v>
+      </x:c>
+      <x:c r="B11" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="str">
+        <x:v>sigungu</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
+        <x:v>sigungu.area_code</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H11" s="37" t="str">
+        <x:v>시도 소속</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-008</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places.created_by</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사용자 장소</x:t>
-        </x:is>
+      <x:c r="A12" s="37" t="str">
+        <x:v>REL-008</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C12" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="str">
+        <x:v>places.area_code</x:v>
+      </x:c>
+      <x:c r="F12" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G12" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H12" s="37" t="str">
+        <x:v>장소 지역</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-009</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_details</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:0..1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_details.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지연 적재 상세</x:t>
-        </x:is>
+      <x:c r="A13" s="37" t="str">
+        <x:v>REL-009</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="str">
+        <x:v>places.created_by</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G13" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H13" s="37" t="str">
+        <x:v>사용자 장소 생성자</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-010</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT/익명화</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">게시글 작성자</x:t>
-        </x:is>
+      <x:c r="A14" s="37" t="str">
+        <x:v>REL-010</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C14" s="37" t="str">
+        <x:v>place_details</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="str">
+        <x:v>place_details.place_id</x:v>
+      </x:c>
+      <x:c r="F14" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G14" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H14" s="37" t="str">
+        <x:v>언어별 상세</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-011</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장소 필수</x:t>
-        </x:is>
+      <x:c r="A15" s="37" t="str">
+        <x:v>REL-011</x:v>
+      </x:c>
+      <x:c r="B15" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="str">
+        <x:v>posts.user_id</x:v>
+      </x:c>
+      <x:c r="F15" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G15" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H15" s="37" t="str">
+        <x:v>게시글 작성자</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-012</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts.event_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이벤트 참여 게시글</x:t>
-        </x:is>
+      <x:c r="A16" s="37" t="str">
+        <x:v>REL-012</x:v>
+      </x:c>
+      <x:c r="B16" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C16" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="D16" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E16" s="37" t="str">
+        <x:v>posts.place_id</x:v>
+      </x:c>
+      <x:c r="F16" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G16" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H16" s="37" t="str">
+        <x:v>게시 장소</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-013</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">서버 산출 지역</x:t>
-        </x:is>
+      <x:c r="A17" s="37" t="str">
+        <x:v>REL-013</x:v>
+      </x:c>
+      <x:c r="B17" s="37" t="str">
+        <x:v>events</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E17" s="37" t="str">
+        <x:v>posts.event_id</x:v>
+      </x:c>
+      <x:c r="F17" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G17" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H17" s="37" t="str">
+        <x:v>행사 참여</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-014</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_images</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_images.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE(30일 지연)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최대 4장</x:t>
-        </x:is>
+      <x:c r="A18" s="37" t="str">
+        <x:v>REL-014</x:v>
+      </x:c>
+      <x:c r="B18" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C18" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="D18" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E18" s="37" t="str">
+        <x:v>posts.area_code</x:v>
+      </x:c>
+      <x:c r="F18" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G18" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H18" s="37" t="str">
+        <x:v>게시 지역</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-015</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">판정 감사</x:t>
-        </x:is>
+      <x:c r="A19" s="37" t="str">
+        <x:v>REL-015</x:v>
+      </x:c>
+      <x:c r="B19" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="str">
+        <x:v>post_images</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E19" s="37" t="str">
+        <x:v>post_images.post_id</x:v>
+      </x:c>
+      <x:c r="F19" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G19" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H19" s="37" t="str">
+        <x:v>게시글 사진</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-016</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE/정책</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">댓글</x:t>
-        </x:is>
+      <x:c r="A20" s="37" t="str">
+        <x:v>REL-016</x:v>
+      </x:c>
+      <x:c r="B20" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C20" s="37" t="str">
+        <x:v>comments</x:v>
+      </x:c>
+      <x:c r="D20" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E20" s="37" t="str">
+        <x:v>comments.post_id</x:v>
+      </x:c>
+      <x:c r="F20" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G20" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H20" s="37" t="str">
+        <x:v>댓글 게시글</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-017</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT/익명화</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">댓글 작성자</x:t>
-        </x:is>
+      <x:c r="A21" s="37" t="str">
+        <x:v>REL-017</x:v>
+      </x:c>
+      <x:c r="B21" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C21" s="37" t="str">
+        <x:v>comments</x:v>
+      </x:c>
+      <x:c r="D21" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E21" s="37" t="str">
+        <x:v>comments.user_id</x:v>
+      </x:c>
+      <x:c r="F21" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G21" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H21" s="37" t="str">
+        <x:v>댓글 작성자</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-018</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments.parent_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">깊이 1</x:t>
-        </x:is>
+      <x:c r="A22" s="37" t="str">
+        <x:v>REL-018</x:v>
+      </x:c>
+      <x:c r="B22" s="37" t="str">
+        <x:v>comments</x:v>
+      </x:c>
+      <x:c r="C22" s="37" t="str">
+        <x:v>comments</x:v>
+      </x:c>
+      <x:c r="D22" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E22" s="37" t="str">
+        <x:v>comments.parent_id</x:v>
+      </x:c>
+      <x:c r="F22" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G22" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H22" s="37" t="str">
+        <x:v>대댓글</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-019</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">likes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">likes.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">좋아요 주체</x:t>
-        </x:is>
+      <x:c r="A23" s="37" t="str">
+        <x:v>REL-019</x:v>
+      </x:c>
+      <x:c r="B23" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C23" s="37" t="str">
+        <x:v>likes</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E23" s="37" t="str">
+        <x:v>likes.user_id</x:v>
+      </x:c>
+      <x:c r="F23" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G23" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H23" s="37" t="str">
+        <x:v>좋아요 주체</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-020</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts/comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">likes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">target_type+target_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">애플리케이션</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">다형 대상, DB FK 불가</x:t>
-        </x:is>
+      <x:c r="A24" s="37" t="str">
+        <x:v>REL-020</x:v>
+      </x:c>
+      <x:c r="B24" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C24" s="37" t="str">
+        <x:v>bookmarks</x:v>
+      </x:c>
+      <x:c r="D24" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E24" s="37" t="str">
+        <x:v>bookmarks.user_id</x:v>
+      </x:c>
+      <x:c r="F24" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G24" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H24" s="37" t="str">
+        <x:v>북마크 주체</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-021</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bookmarks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bookmarks.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">저장 주체</x:t>
-        </x:is>
+      <x:c r="A25" s="37" t="str">
+        <x:v>REL-021</x:v>
+      </x:c>
+      <x:c r="B25" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C25" s="37" t="str">
+        <x:v>post_tags</x:v>
+      </x:c>
+      <x:c r="D25" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E25" s="37" t="str">
+        <x:v>post_tags.post_id</x:v>
+      </x:c>
+      <x:c r="F25" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G25" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H25" s="37" t="str">
+        <x:v>게시글 태그</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-022</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts/places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bookmarks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">target_type+target_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">애플리케이션</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">대상 존재 검증</x:t>
-        </x:is>
+      <x:c r="A26" s="37" t="str">
+        <x:v>REL-022</x:v>
+      </x:c>
+      <x:c r="B26" s="37" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="C26" s="37" t="str">
+        <x:v>post_tags</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E26" s="37" t="str">
+        <x:v>post_tags.tag_id</x:v>
+      </x:c>
+      <x:c r="F26" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G26" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H26" s="37" t="str">
+        <x:v>태그 사전</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-023</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_tags.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">태그 연결</x:t>
-        </x:is>
+      <x:c r="A27" s="37" t="str">
+        <x:v>REL-023</x:v>
+      </x:c>
+      <x:c r="B27" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C27" s="37" t="str">
+        <x:v>events</x:v>
+      </x:c>
+      <x:c r="D27" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E27" s="37" t="str">
+        <x:v>events.area_code</x:v>
+      </x:c>
+      <x:c r="F27" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G27" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H27" s="37" t="str">
+        <x:v>행사 지역</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-024</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_tags.tag_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">태그 사전</x:t>
-        </x:is>
+      <x:c r="A28" s="37" t="str">
+        <x:v>REL-024</x:v>
+      </x:c>
+      <x:c r="B28" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C28" s="37" t="str">
+        <x:v>events</x:v>
+      </x:c>
+      <x:c r="D28" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E28" s="37" t="str">
+        <x:v>events.place_id</x:v>
+      </x:c>
+      <x:c r="F28" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G28" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H28" s="37" t="str">
+        <x:v>행사 장소</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-025</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이벤트 지역</x:t>
-        </x:is>
+      <x:c r="A29" s="37" t="str">
+        <x:v>REL-025</x:v>
+      </x:c>
+      <x:c r="B29" s="37" t="str">
+        <x:v>events</x:v>
+      </x:c>
+      <x:c r="C29" s="37" t="str">
+        <x:v>badges</x:v>
+      </x:c>
+      <x:c r="D29" s="37" t="str">
+        <x:v>1:0..1</x:v>
+      </x:c>
+      <x:c r="E29" s="37" t="str">
+        <x:v>badges.event_id</x:v>
+      </x:c>
+      <x:c r="F29" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G29" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H29" s="37" t="str">
+        <x:v>행사 뱃지</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-026</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이벤트 장소</x:t>
-        </x:is>
+      <x:c r="A30" s="37" t="str">
+        <x:v>REL-026</x:v>
+      </x:c>
+      <x:c r="B30" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C30" s="37" t="str">
+        <x:v>badges</x:v>
+      </x:c>
+      <x:c r="D30" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E30" s="37" t="str">
+        <x:v>badges.area_code</x:v>
+      </x:c>
+      <x:c r="F30" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G30" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H30" s="37" t="str">
+        <x:v>지역 뱃지</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="33" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-027</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:0..1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges.event_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">순환 FK 방지를 위해 badges가 소유</x:t>
-        </x:is>
+      <x:c r="A31" s="37" t="str">
+        <x:v>REL-027</x:v>
+      </x:c>
+      <x:c r="B31" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C31" s="37" t="str">
+        <x:v>user_badges</x:v>
+      </x:c>
+      <x:c r="D31" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E31" s="37" t="str">
+        <x:v>user_badges.user_id</x:v>
+      </x:c>
+      <x:c r="F31" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G31" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H31" s="37" t="str">
+        <x:v>획득 사용자</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-028</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지역 뱃지</x:t>
-        </x:is>
+      <x:c r="A32" s="37" t="str">
+        <x:v>REL-028</x:v>
+      </x:c>
+      <x:c r="B32" s="37" t="str">
+        <x:v>badges</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="str">
+        <x:v>user_badges</x:v>
+      </x:c>
+      <x:c r="D32" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E32" s="37" t="str">
+        <x:v>user_badges.badge_id</x:v>
+      </x:c>
+      <x:c r="F32" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G32" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H32" s="37" t="str">
+        <x:v>획득 뱃지</x:v>
       </x:c>
     </x:row>
     <x:row r="33" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-029</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사용자 수집</x:t>
-        </x:is>
+      <x:c r="A33" s="37" t="str">
+        <x:v>REL-029</x:v>
+      </x:c>
+      <x:c r="B33" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C33" s="37" t="str">
+        <x:v>user_badges</x:v>
+      </x:c>
+      <x:c r="D33" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E33" s="37" t="str">
+        <x:v>user_badges.source_post_id</x:v>
+      </x:c>
+      <x:c r="F33" s="37" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="G33" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H33" s="37" t="str">
+        <x:v>지급 근거</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-030</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges.badge_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">뱃지 획득</x:t>
-        </x:is>
+      <x:c r="A34" s="37" t="str">
+        <x:v>REL-030</x:v>
+      </x:c>
+      <x:c r="B34" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C34" s="37" t="str">
+        <x:v>post_rankings</x:v>
+      </x:c>
+      <x:c r="D34" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E34" s="37" t="str">
+        <x:v>post_rankings.post_id</x:v>
+      </x:c>
+      <x:c r="F34" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G34" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H34" s="37" t="str">
+        <x:v>게시글 순위</x:v>
       </x:c>
     </x:row>
     <x:row r="35" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-031</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges.source_post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지급 근거</x:t>
-        </x:is>
+      <x:c r="A35" s="37" t="str">
+        <x:v>REL-031</x:v>
+      </x:c>
+      <x:c r="B35" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C35" s="37" t="str">
+        <x:v>visits</x:v>
+      </x:c>
+      <x:c r="D35" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E35" s="37" t="str">
+        <x:v>visits.user_id</x:v>
+      </x:c>
+      <x:c r="F35" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G35" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H35" s="37" t="str">
+        <x:v>방문 사용자</x:v>
       </x:c>
     </x:row>
     <x:row r="36" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-032</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">방문 사용자</x:t>
-        </x:is>
+      <x:c r="A36" s="37" t="str">
+        <x:v>REL-032</x:v>
+      </x:c>
+      <x:c r="B36" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="str">
+        <x:v>visits</x:v>
+      </x:c>
+      <x:c r="D36" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E36" s="37" t="str">
+        <x:v>visits.place_id</x:v>
+      </x:c>
+      <x:c r="F36" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G36" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H36" s="37" t="str">
+        <x:v>방문 장소</x:v>
       </x:c>
     </x:row>
     <x:row r="37" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-033</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">방문 장소</x:t>
-        </x:is>
+      <x:c r="A37" s="37" t="str">
+        <x:v>REL-033</x:v>
+      </x:c>
+      <x:c r="B37" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C37" s="37" t="str">
+        <x:v>visits</x:v>
+      </x:c>
+      <x:c r="D37" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E37" s="37" t="str">
+        <x:v>visits.post_id</x:v>
+      </x:c>
+      <x:c r="F37" s="37" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="G37" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H37" s="37" t="str">
+        <x:v>방문 근거</x:v>
       </x:c>
     </x:row>
     <x:row r="38" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-034</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:0..1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">방문 발생 게시글</x:t>
-        </x:is>
+      <x:c r="A38" s="37" t="str">
+        <x:v>REL-034</x:v>
+      </x:c>
+      <x:c r="B38" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C38" s="37" t="str">
+        <x:v>heatmap_cells</x:v>
+      </x:c>
+      <x:c r="D38" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E38" s="37" t="str">
+        <x:v>heatmap_cells.top_place_id</x:v>
+      </x:c>
+      <x:c r="F38" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G38" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H38" s="37" t="str">
+        <x:v>대표 장소</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-035</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">heatmap_cells</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">heatmap_cells.top_place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H39" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">셀 대표 장소</x:t>
-        </x:is>
+      <x:c r="A39" s="37" t="str">
+        <x:v>REL-035</x:v>
+      </x:c>
+      <x:c r="B39" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C39" s="37" t="str">
+        <x:v>region_stats</x:v>
+      </x:c>
+      <x:c r="D39" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E39" s="37" t="str">
+        <x:v>region_stats.area_code</x:v>
+      </x:c>
+      <x:c r="F39" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G39" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H39" s="37" t="str">
+        <x:v>지역 집계</x:v>
       </x:c>
     </x:row>
     <x:row r="40" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-036</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">heatmap_cells</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">N:M</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sample_post_ids</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">애플리케이션</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H40" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최대 10개 배열, FK 없음</x:t>
-        </x:is>
+      <x:c r="A40" s="37" t="str">
+        <x:v>REL-036</x:v>
+      </x:c>
+      <x:c r="B40" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C40" s="37" t="str">
+        <x:v>place_rankings</x:v>
+      </x:c>
+      <x:c r="D40" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E40" s="37" t="str">
+        <x:v>place_rankings.place_id</x:v>
+      </x:c>
+      <x:c r="F40" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G40" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H40" s="37" t="str">
+        <x:v>장소 순위</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-037</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">region_stats</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">region_stats.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기간별 지역 집계</x:t>
-        </x:is>
+      <x:c r="A41" s="37" t="str">
+        <x:v>REL-037</x:v>
+      </x:c>
+      <x:c r="B41" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C41" s="37" t="str">
+        <x:v>place_rankings</x:v>
+      </x:c>
+      <x:c r="D41" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E41" s="37" t="str">
+        <x:v>place_rankings.area_code</x:v>
+      </x:c>
+      <x:c r="F41" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G41" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H41" s="37" t="str">
+        <x:v>지역별 순위</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-038</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_rankings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_rankings.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기간·테마별 랭킹</x:t>
-        </x:is>
+      <x:c r="A42" s="37" t="str">
+        <x:v>REL-038</x:v>
+      </x:c>
+      <x:c r="B42" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C42" s="37" t="str">
+        <x:v>notifications</x:v>
+      </x:c>
+      <x:c r="D42" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E42" s="37" t="str">
+        <x:v>notifications.recipient_id</x:v>
+      </x:c>
+      <x:c r="F42" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G42" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H42" s="37" t="str">
+        <x:v>알림 수신자</x:v>
       </x:c>
     </x:row>
     <x:row r="43" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-039</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_rankings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_rankings.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지역 랭킹</x:t>
-        </x:is>
+      <x:c r="A43" s="37" t="str">
+        <x:v>REL-039</x:v>
+      </x:c>
+      <x:c r="B43" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C43" s="37" t="str">
+        <x:v>notifications</x:v>
+      </x:c>
+      <x:c r="D43" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E43" s="37" t="str">
+        <x:v>notifications.actor_id</x:v>
+      </x:c>
+      <x:c r="F43" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G43" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H43" s="37" t="str">
+        <x:v>알림 행위자</x:v>
       </x:c>
     </x:row>
     <x:row r="44" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-040</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications.recipient_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H44" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">수신자</x:t>
-        </x:is>
+      <x:c r="A44" s="37" t="str">
+        <x:v>REL-040</x:v>
+      </x:c>
+      <x:c r="B44" s="37" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C44" s="37" t="str">
+        <x:v>reports</x:v>
+      </x:c>
+      <x:c r="D44" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E44" s="37" t="str">
+        <x:v>reports.reporter_id</x:v>
+      </x:c>
+      <x:c r="F44" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G44" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H44" s="37" t="str">
+        <x:v>신고자</x:v>
       </x:c>
     </x:row>
     <x:row r="45" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-041</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications.actor_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H45" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">행위자</x:t>
-        </x:is>
+      <x:c r="A45" s="37" t="str">
+        <x:v>REL-041</x:v>
+      </x:c>
+      <x:c r="B45" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C45" s="37" t="str">
+        <x:v>sync_logs</x:v>
+      </x:c>
+      <x:c r="D45" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E45" s="37" t="str">
+        <x:v>sync_logs.area_code</x:v>
+      </x:c>
+      <x:c r="F45" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G45" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H45" s="37" t="str">
+        <x:v>동기화 지역</x:v>
       </x:c>
     </x:row>
     <x:row r="46" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-042</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts/users/badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">target_type+target_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">애플리케이션</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">알림 이동 대상</x:t>
-        </x:is>
+      <x:c r="A46" s="37" t="str">
+        <x:v>REL-042</x:v>
+      </x:c>
+      <x:c r="B46" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C46" s="37" t="str">
+        <x:v>search_logs</x:v>
+      </x:c>
+      <x:c r="D46" s="37" t="str">
+        <x:v>1:N</x:v>
+      </x:c>
+      <x:c r="E46" s="37" t="str">
+        <x:v>search_logs.area_code</x:v>
+      </x:c>
+      <x:c r="F46" s="37" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G46" s="37" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="H46" s="37" t="str">
+        <x:v>검색 지역</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-043</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reports</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reports.reporter_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RESTRICT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H47" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">신고자</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A47" s="37"/>
+      <x:c r="B47" s="37"/>
+      <x:c r="C47" s="37"/>
+      <x:c r="D47" s="37"/>
+      <x:c r="E47" s="37"/>
+      <x:c r="F47" s="37"/>
+      <x:c r="G47" s="37"/>
+      <x:c r="H47" s="37"/>
     </x:row>
     <x:row r="48" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
-      <x:c r="A48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-044</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts/places/comments/users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reports</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">target_type+target_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">애플리케이션</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H48" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">신고 대상</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A48" s="37"/>
+      <x:c r="B48" s="37"/>
+      <x:c r="C48" s="37"/>
+      <x:c r="D48" s="37"/>
+      <x:c r="E48" s="37"/>
+      <x:c r="F48" s="37"/>
+      <x:c r="G48" s="37"/>
+      <x:c r="H48" s="37"/>
     </x:row>
     <x:row r="49" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-045</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최근 검색</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A49" s="37"/>
+      <x:c r="B49" s="37"/>
+      <x:c r="C49" s="37"/>
+      <x:c r="D49" s="37"/>
+      <x:c r="E49" s="37"/>
+      <x:c r="F49" s="37"/>
+      <x:c r="G49" s="37"/>
+      <x:c r="H49" s="37"/>
     </x:row>
     <x:row r="50" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-046</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H50" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지역별 인기 검색</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A50" s="37"/>
+      <x:c r="B50" s="37"/>
+      <x:c r="C50" s="37"/>
+      <x:c r="D50" s="37"/>
+      <x:c r="E50" s="37"/>
+      <x:c r="F50" s="37"/>
+      <x:c r="G50" s="37"/>
+      <x:c r="H50" s="37"/>
     </x:row>
     <x:row r="51" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sigungu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sigungu.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H51" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시도 → 시군구 마스터</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A51" s="37"/>
+      <x:c r="B51" s="37"/>
+      <x:c r="C51" s="37"/>
+      <x:c r="D51" s="37"/>
+      <x:c r="E51" s="37"/>
+      <x:c r="F51" s="37"/>
+      <x:c r="G51" s="37"/>
+      <x:c r="H51" s="37"/>
     </x:row>
     <x:row r="52" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-048</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sigungu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places.(area_code, sigungu_code)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SET NULL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Logical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H52" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">복합 참조 — 다이어그램 선은 생략</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A52" s="37"/>
+      <x:c r="B52" s="37"/>
+      <x:c r="C52" s="37"/>
+      <x:c r="D52" s="37"/>
+      <x:c r="E52" s="37"/>
+      <x:c r="F52" s="37"/>
+      <x:c r="G52" s="37"/>
+      <x:c r="H52" s="37"/>
     </x:row>
     <x:row r="53" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
-      <x:c r="A53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REL-049</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_rankings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1:0..N</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_rankings.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CASCADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Physical</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H53" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기간별 게시글 인기 집계</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A53" s="37"/>
+      <x:c r="B53" s="37"/>
+      <x:c r="C53" s="37"/>
+      <x:c r="D53" s="37"/>
+      <x:c r="E53" s="37"/>
+      <x:c r="F53" s="37"/>
+      <x:c r="G53" s="37"/>
+      <x:c r="H53" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4102,7 +3184,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf73af39d33f442f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc654fc8c17bf45a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7011,11 +6093,9 @@
           <x:t xml:space="preserve">PST-001~006, PST-008~011, PST-016~032, EVT-016~023, VST-001~002, BDG-005~006</x:t>
         </x:is>
       </x:c>
-      <x:c r="P38" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts, post_images, post_tags, tier_logs, visits, user_badges
-※ eventId가 있으면 고정 태그를 서버가 재주입; 반경 밖이어도 게시 성공·badgeAwarded=false</x:t>
-        </x:is>
+      <x:c r="P38" s="37" t="str">
+        <x:v>posts, post_images, post_tags, visits, user_badges
+※ eventId가 있으면 고정 태그를 서버가 재주입; 반경 밖이어도 게시 성공·badgeAwarded=false</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
@@ -7258,10 +6338,8 @@
           <x:t xml:space="preserve">PST-033, PST-042, PST-046~047, SYS-010</x:t>
         </x:is>
       </x:c>
-      <x:c r="P41" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts, post_images, post_tags, users, places, tier_logs</x:t>
-        </x:is>
+      <x:c r="P41" s="37" t="str">
+        <x:v>posts, post_images, post_tags, users, places</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="33" customFormat="1" ht="86.4000015258789" customHeight="1">
@@ -12205,7 +11283,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf84033cc290b433f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67f956d6004945ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24296,7 +23374,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35b035f390cb48c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ec598875e54713"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26792,10 +25870,8 @@
           <x:t xml:space="preserve">MEDIUM</x:t>
         </x:is>
       </x:c>
-      <x:c r="G71" s="46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts/tier_logs</x:t>
-        </x:is>
+      <x:c r="G71" s="46" t="str">
+        <x:v>posts</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -26827,10 +25903,8 @@
       <x:c r="F72" s="37" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G72" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
+      <x:c r="G72" s="37" t="str">
+        <x:v>posts/places</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -26862,10 +25936,8 @@
       <x:c r="F73" s="37" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="G73" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places/events/regions</x:t>
-        </x:is>
+      <x:c r="G73" s="37" t="str">
+        <x:v>places/events/regions</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -26899,10 +25971,8 @@
           <x:t xml:space="preserve">WITHIN_RADIUS_30D</x:t>
         </x:is>
       </x:c>
-      <x:c r="G74" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
+      <x:c r="G74" s="37" t="str">
+        <x:v>계산값</x:v>
       </x:c>
     </x:row>
     <x:row r="75" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -26936,10 +26006,8 @@
           <x:t xml:space="preserve">{days:2}</x:t>
         </x:is>
       </x:c>
-      <x:c r="G75" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
+      <x:c r="G75" s="37" t="str">
+        <x:v>계산값</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -27697,10 +26765,8 @@
           <x:t xml:space="preserve">{...}</x:t>
         </x:is>
       </x:c>
-      <x:c r="G96" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
+      <x:c r="G96" s="37" t="str">
+        <x:v>posts/places</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="33" customFormat="1" ht="15" customHeight="1">
@@ -33068,10 +32134,8 @@
           <x:t xml:space="preserve">{...}</x:t>
         </x:is>
       </x:c>
-      <x:c r="G245" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
+      <x:c r="G245" s="37" t="str">
+        <x:v>posts/places</x:v>
       </x:c>
     </x:row>
     <x:row r="246" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
@@ -36195,7 +35259,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R679189f07aa743e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb159703a09a24102"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36851,7 +35915,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72c3953997264500"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf4037cd02f74f3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38557,7 +37621,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5924b40c0744117"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e4e96357354eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39185,7 +38249,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67845ebd5f74472a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba54ab3ab10e45c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52157,7 +51221,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd0b72a1c83848aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646cc4da6ffe4c8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52192,1406 +51256,856 @@
       </x:c>
     </x:row>
     <x:row r="4" s="33" customFormat="1" ht="26.399999618530273" customHeight="1">
-      <x:c r="A4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">도메인</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">테이블</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Unique</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">주요 컬럼</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">삭제·보존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">관련 요구사항</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설계 메모</x:t>
-        </x:is>
+      <x:c r="A4" s="32" t="str">
+        <x:v>도메인</x:v>
+      </x:c>
+      <x:c r="B4" s="32" t="str">
+        <x:v>테이블</x:v>
+      </x:c>
+      <x:c r="C4" s="32" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E4" s="32" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F4" s="32" t="str">
+        <x:v>주요 컬럼</x:v>
+      </x:c>
+      <x:c r="G4" s="32" t="str">
+        <x:v>삭제·보존</x:v>
+      </x:c>
+      <x:c r="H4" s="32" t="str">
+        <x:v>관련 요구사항</x:v>
+      </x:c>
+      <x:c r="I4" s="32" t="str">
+        <x:v>설계 메모</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="33" customFormat="1" ht="259.20001220703125" customHeight="1">
-      <x:c r="A5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">계정</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id (uuid)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(provider, provider_user_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">provider, provider_user_id, email, nickname(20), profile_image_url, bio(200), locale, role, status, upload_blocked_until, push_like_enabled, push_follow_enabled, push_badge_enabled, terms_agreed_at, badge_count, follower_count, following_count, post_count, withdrawn_at, purge_scheduled_at, restore_key</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-001, AUTH-014, USER-001~023, PST-032</x:t>
-        </x:is>
+      <x:c r="A5" s="40" t="str">
+        <x:v>계정</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>(provider, provider_user_id)</x:v>
+      </x:c>
+      <x:c r="F5" s="40" t="str">
+        <x:v>provider, provider_user_id, email, nickname, profile_image_url, bio, locale, role, status, upload_blocked_until, push_like_enabled, push_follow_enabled, push_badge_enabled, badge_count, follower_count, following_count, post_count, withdrawn_at, purge_scheduled_at, restore_key, created_at, updated_at</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="str">
+        <x:v>논리</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="str">
+        <x:v>AUTH-001, AUTH-014, USER-001~023, PST-032</x:v>
       </x:c>
       <x:c r="I5" s="40" t="str">
-        <x:v>DBML v1.1.3 정합. terms_agreed_at만 보강(USER-006 근거, DBML 미포함) PK 는 uuid — 구현된 V1__auth_schema.sql 기준 (v1.1.5 정정).</x:v>
+        <x:v>Google OAuth 단일. role은 회원 등급이 아니라 관리자 권한 구분</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">계정</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_devices</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">device_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(user_id, device_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fcm_token, platform, app_version</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">USER-007, NTF-010</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사용자별 복수 기기</x:t>
-        </x:is>
+      <x:c r="A6" s="37" t="str">
+        <x:v>계정</x:v>
+      </x:c>
+      <x:c r="B6" s="37" t="str">
+        <x:v>user_devices</x:v>
+      </x:c>
+      <x:c r="C6" s="37" t="str">
+        <x:v>device_id</x:v>
+      </x:c>
+      <x:c r="D6" s="37" t="str">
+        <x:v>user_id→users.user_id</x:v>
+      </x:c>
+      <x:c r="E6" s="37" t="str">
+        <x:v>(user_id, fcm_token)</x:v>
+      </x:c>
+      <x:c r="F6" s="37" t="str">
+        <x:v>fcm_token, platform, app_version, updated_at</x:v>
+      </x:c>
+      <x:c r="G6" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H6" s="37" t="str">
+        <x:v>USER-007, NTF-010</x:v>
+      </x:c>
+      <x:c r="I6" s="37" t="str">
+        <x:v>앱 시작마다 등록·갱신</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="33" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">계정</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refresh_tokens</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">token_hash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users, device_id→user_devices</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">token_hash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">expires_at, revoked_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-007~009</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">원문 미저장</x:t>
-        </x:is>
+      <x:c r="A7" s="37" t="str">
+        <x:v>계정</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>refresh_tokens</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>token_hash</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>user_id→users, device_id→user_devices</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>expires_at, revoked_at</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>AUTH-007~009</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="str">
+        <x:v>원문 대신 SHA-256 해시만 저장하고 사용 시 회전</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">계정</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">account_deletion_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">log_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users.user_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reason, content_action, purged_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">감사 보존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">USER-015, USER-019</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DBML v1.1.3 정합 — 대리키 PK</x:t>
-        </x:is>
+      <x:c r="A8" s="37" t="str">
+        <x:v>계정</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>account_deletion_logs</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="str">
+        <x:v>log_id</x:v>
+      </x:c>
+      <x:c r="D8" s="37" t="str">
+        <x:v>user_id→users.user_id</x:v>
+      </x:c>
+      <x:c r="E8" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F8" s="37" t="str">
+        <x:v>reason, content_action, deleted_at, purged_at</x:v>
+      </x:c>
+      <x:c r="G8" s="37" t="str">
+        <x:v>감사 보존</x:v>
+      </x:c>
+      <x:c r="H8" s="37" t="str">
+        <x:v>USER-015, USER-019</x:v>
+      </x:c>
+      <x:c r="I8" s="37" t="str">
+        <x:v>탈퇴 접수와 물리 삭제 완료 시각 기록</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">소셜</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follows</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(follower_id, following_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">follower_id→users, following_id→users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SOC-001~009</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">자기 자신 CHECK 차단</x:t>
-        </x:is>
+      <x:c r="A9" s="37" t="str">
+        <x:v>소셜</x:v>
+      </x:c>
+      <x:c r="B9" s="37" t="str">
+        <x:v>follows</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>(follower_id, following_id)</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>follower_id→users, following_id→users</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>SOC-001~009</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="str">
+        <x:v>복합 PK로 중복 방지</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="33" customFormat="1" ht="118.80000305175781" customHeight="1">
-      <x:c r="A10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장소</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name_ko, name_en, representative_image_url, default_event_verify_radius_m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기준정보</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-001~002, MAP-006</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">17개 시도 마스터. area_code를 단독 PK로 둬야 다른 8개 테이블의 area_code FK가 성립한다 (DBML v1.1.3)</x:t>
-        </x:is>
+      <x:c r="A10" s="37" t="str">
+        <x:v>장소</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="str">
+        <x:v>regions</x:v>
+      </x:c>
+      <x:c r="C10" s="37" t="str">
+        <x:v>area_code</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F10" s="37" t="str">
+        <x:v>name_ko, name_en, representative_image_url, default_event_verify_radius_m</x:v>
+      </x:c>
+      <x:c r="G10" s="37" t="str">
+        <x:v>기준정보</x:v>
+      </x:c>
+      <x:c r="H10" s="37" t="str">
+        <x:v>PLC-001~002, MAP-006, PLC-022</x:v>
+      </x:c>
+      <x:c r="I10" s="37" t="str">
+        <x:v>17개 시도 마스터. TourAPI areaCode를 그대로 사용</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="33" customFormat="1" ht="118.80000305175781" customHeight="1">
-      <x:c r="A11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장소</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sigungu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(area_code, sigungu_code)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions.area_code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name_ko, name_en</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기준정보</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-002, PLC-020</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">areaCode 오퍼레이션으로 적재하는 시군구 마스터 (DBML v1.1.3)</x:t>
-        </x:is>
+      <x:c r="A11" s="37" t="str">
+        <x:v>장소</x:v>
+      </x:c>
+      <x:c r="B11" s="37" t="str">
+        <x:v>sigungu</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="str">
+        <x:v>(area_code, sigungu_code)</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>area_code→regions.area_code</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="str">
+        <x:v>name_ko, name_en</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="str">
+        <x:v>기준정보</x:v>
+      </x:c>
+      <x:c r="H11" s="37" t="str">
+        <x:v>PLC-002, PLC-020</x:v>
+      </x:c>
+      <x:c r="I11" s="37" t="str">
+        <x:v>TourAPI 시군구 마스터</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="33" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장소</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions, (area_code, sigungu_code)→sigungu, created_by→users</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(content_id, content_type_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_type, content_id, content_type_id, title, addr1, geom, verify_radius_m, area_code, sigungu_code, has_coordinate, post_count, visit_count, view_count, status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-003~023, PLC-014</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">공간 GiST 인덱스 필수. status만 보강(PLC-023 장소 숨김 근거, DBML 미포함)</x:t>
-        </x:is>
+      <x:c r="A12" s="37" t="str">
+        <x:v>장소</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="str">
+        <x:v>places</x:v>
+      </x:c>
+      <x:c r="C12" s="37" t="str">
+        <x:v>place_id</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="str">
+        <x:v>area_code→regions, (area_code, sigungu_code)→sigungu, created_by→users</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="str">
+        <x:v>content_id</x:v>
+      </x:c>
+      <x:c r="F12" s="37" t="str">
+        <x:v>place_type, content_id, content_type_id, title, addr1, geom, verify_radius_m, area_code, sigungu_code, has_coordinate, post_count, visit_count, view_count, created_by, created_at</x:v>
+      </x:c>
+      <x:c r="G12" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H12" s="37" t="str">
+        <x:v>PLC-003~023</x:v>
+      </x:c>
+      <x:c r="I12" s="37" t="str">
+        <x:v>geom은 nullable geography(Point,4326). GIST·pg_trgm GIN 인덱스 사용</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="33" customFormat="1" ht="162" customHeight="1">
-      <x:c r="A13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장소</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_details</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(place_id, language_code)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_id→places.place_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">language_code, overview, tel, homepage, use_time, rest_date</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">종속</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-006, SYS-012, SYS-018</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">언어별 1행. 요청 언어 상세가 없으면 그 시점에 지연 적재</x:t>
-        </x:is>
+      <x:c r="A13" s="37" t="str">
+        <x:v>장소</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="str">
+        <x:v>place_details</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="str">
+        <x:v>(place_id, language_code)</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="str">
+        <x:v>place_id→places.place_id</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="str">
+        <x:v>overview, tel, homepage, use_time, rest_date</x:v>
+      </x:c>
+      <x:c r="G13" s="37" t="str">
+        <x:v>종속</x:v>
+      </x:c>
+      <x:c r="H13" s="37" t="str">
+        <x:v>PLC-006, SYS-012, SYS-018</x:v>
+      </x:c>
+      <x:c r="I13" s="37" t="str">
+        <x:v>언어별 상세를 최초 조회 시 지연 적재</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="33" customFormat="1" ht="86.4000015258789" customHeight="1">
-      <x:c r="A14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">게시글</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users, place_id→places, event_id→events, area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">content, original_language_code, tier, lat, lng, taken_at, source, area_code, like_count, comment_count, view_count, status, created_at, updated_at, deleted_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-001~049, SYS-010</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">created_at 등 공통 타임스탬프 보강</x:t>
-        </x:is>
+      <x:c r="A14" s="37" t="str">
+        <x:v>게시글</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="str">
+        <x:v>posts</x:v>
+      </x:c>
+      <x:c r="C14" s="37" t="str">
+        <x:v>post_id</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="str">
+        <x:v>user_id→users, place_id→places, event_id→events, area_code→regions</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F14" s="37" t="str">
+        <x:v>content, original_language_code, tier, lat, lng, taken_at, source, like_count, comment_count, view_count, status, created_at, updated_at, deleted_at</x:v>
+      </x:c>
+      <x:c r="G14" s="37" t="str">
+        <x:v>논리</x:v>
+      </x:c>
+      <x:c r="H14" s="37" t="str">
+        <x:v>PST-001~049, SYS-010</x:v>
+      </x:c>
+      <x:c r="I14" s="37" t="str">
+        <x:v>status는 ACTIVE/BLINDED/DELETED. 장소·좌표·등급은 수정 불가</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="33" customFormat="1" ht="86.4000015258789" customHeight="1">
-      <x:c r="A15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">게시글</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_images</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_image_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id→posts.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(post_id, sort_order), (post_id, image_hash)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">image_key, thumbnail_url, aspect_ratio, sort_order, image_hash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-013~021, PST-031</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">게시글당 1~4장</x:t>
-        </x:is>
+      <x:c r="A15" s="37" t="str">
+        <x:v>게시글</x:v>
+      </x:c>
+      <x:c r="B15" s="37" t="str">
+        <x:v>post_images</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="str">
+        <x:v>post_image_id</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="str">
+        <x:v>post_id→posts.post_id</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="str">
+        <x:v>(post_id, sort_order)</x:v>
+      </x:c>
+      <x:c r="F15" s="37" t="str">
+        <x:v>image_key, thumbnail_url, aspect_ratio, sort_order</x:v>
+      </x:c>
+      <x:c r="G15" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H15" s="37" t="str">
+        <x:v>PST-002, PST-021</x:v>
+      </x:c>
+      <x:c r="I15" s="37" t="str">
+        <x:v>최대 4장. sort_order 0이 대표 사진</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
-      <x:c r="A16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">게시글</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier_log_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id→posts.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tier, source, taken_at, has_taken_coordinate, distance_m, applied_radius_m, threshold_high_minutes, threshold_medium_days, decided_reason, decided_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">감사 보존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-022~028</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">판정 근거 감사 로그(1:N). 인덱스 (post_id, decided_at). 현재 등급은 posts.tier, 이유는 최신 1행 (DBML v1.1.3)</x:t>
-        </x:is>
+      <x:c r="A16" s="37" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B16" s="37" t="str">
+        <x:v>comments</x:v>
+      </x:c>
+      <x:c r="C16" s="37" t="str">
+        <x:v>comment_id</x:v>
+      </x:c>
+      <x:c r="D16" s="37" t="str">
+        <x:v>post_id→posts, user_id→users, parent_id→comments</x:v>
+      </x:c>
+      <x:c r="E16" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" s="37" t="str">
+        <x:v>content, like_count, status, created_at</x:v>
+      </x:c>
+      <x:c r="G16" s="37" t="str">
+        <x:v>논리</x:v>
+      </x:c>
+      <x:c r="H16" s="37" t="str">
+        <x:v>CMU-012~017</x:v>
+      </x:c>
+      <x:c r="I16" s="37" t="str">
+        <x:v>대댓글 깊이 1단계</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">커뮤니티</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comment_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id→posts, user_id→users, parent_id→comments</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">content, like_count, status, created_at, updated_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CMU-012~017</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">parent는 최상위 댓글만</x:t>
-        </x:is>
+      <x:c r="A17" s="37" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B17" s="37" t="str">
+        <x:v>likes</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="str">
+        <x:v>(user_id, target_type, target_id)</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
+        <x:v>user_id→users; target는 논리 FK</x:v>
+      </x:c>
+      <x:c r="E17" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F17" s="37" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="G17" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H17" s="37" t="str">
+        <x:v>PST-040~041, CMU-018</x:v>
+      </x:c>
+      <x:c r="I17" s="37" t="str">
+        <x:v>POST/COMMENT 다형 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">커뮤니티</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">likes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(user_id, target_type, target_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users; target는 논리 FK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-040, CMU-018</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">POST/COMMENT 다형 대상</x:t>
-        </x:is>
+      <x:c r="A18" s="37" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B18" s="37" t="str">
+        <x:v>bookmarks</x:v>
+      </x:c>
+      <x:c r="C18" s="37" t="str">
+        <x:v>(user_id, target_type, target_id)</x:v>
+      </x:c>
+      <x:c r="D18" s="37" t="str">
+        <x:v>user_id→users; target는 논리 FK</x:v>
+      </x:c>
+      <x:c r="E18" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F18" s="37" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="G18" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H18" s="37" t="str">
+        <x:v>PLC-015, CMU-023~024</x:v>
+      </x:c>
+      <x:c r="I18" s="37" t="str">
+        <x:v>POST/PLACE 다형 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="33" customFormat="1" ht="75.5999984741211" customHeight="1">
-      <x:c r="A19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">커뮤니티</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bookmarks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(user_id, target_type, target_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users; target는 논리 FK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-015, CMU-023~024</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">POST/PLACE 다형 대상</x:t>
-        </x:is>
+      <x:c r="A19" s="37" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B19" s="37" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="str">
+        <x:v>tag_id</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E19" s="37" t="str">
+        <x:v>normalized_name</x:v>
+      </x:c>
+      <x:c r="F19" s="37" t="str">
+        <x:v>name, theme_code, usage_count</x:v>
+      </x:c>
+      <x:c r="G19" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H19" s="37" t="str">
+        <x:v>CMU-025~031, RNK-005</x:v>
+      </x:c>
+      <x:c r="I19" s="37" t="str">
+        <x:v>normalized_name으로 중복 방지</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
-      <x:c r="A20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">커뮤니티</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tag_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">normalized_name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name, normalized_name, theme_code, usage_count</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CMU-025~031, RNK-005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사용자 K-컬처 태그 원천</x:t>
-        </x:is>
+      <x:c r="A20" s="37" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B20" s="37" t="str">
+        <x:v>post_tags</x:v>
+      </x:c>
+      <x:c r="C20" s="37" t="str">
+        <x:v>(post_id, tag_id)</x:v>
+      </x:c>
+      <x:c r="D20" s="37" t="str">
+        <x:v>post_id→posts, tag_id→tags</x:v>
+      </x:c>
+      <x:c r="E20" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F20" s="37" t="str">
+        <x:v>is_locked, is_suggested</x:v>
+      </x:c>
+      <x:c r="G20" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H20" s="37" t="str">
+        <x:v>PST-004, CMU-029~032</x:v>
+      </x:c>
+      <x:c r="I20" s="37" t="str">
+        <x:v>행사 고정 태그와 추천 채택 여부 기록</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="33" customFormat="1" ht="129.60000610351562" customHeight="1">
-      <x:c r="A21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">커뮤니티</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(post_id, tag_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id→posts, tag_id→tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">is_locked, is_suggested, created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-004, CMU-029~032</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">원본의 tags/post_tags를 물리 2개로 분리</x:t>
-        </x:is>
+      <x:c r="A21" s="37" t="str">
+        <x:v>이벤트</x:v>
+      </x:c>
+      <x:c r="B21" s="37" t="str">
+        <x:v>events</x:v>
+      </x:c>
+      <x:c r="C21" s="37" t="str">
+        <x:v>event_id</x:v>
+      </x:c>
+      <x:c r="D21" s="37" t="str">
+        <x:v>area_code→regions, place_id→places</x:v>
+      </x:c>
+      <x:c r="E21" s="37" t="str">
+        <x:v>content_id</x:v>
+      </x:c>
+      <x:c r="F21" s="37" t="str">
+        <x:v>title, overview, start_date, end_date, thumbnail_url, fixed_tags, participant_count, source, verify_radius_m</x:v>
+      </x:c>
+      <x:c r="G21" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H21" s="37" t="str">
+        <x:v>EVT-001~023</x:v>
+      </x:c>
+      <x:c r="I21" s="37" t="str">
+        <x:v>인증 반경은 이벤트값→지역 기본값→2,000m</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="33" customFormat="1" ht="129.60000610351562" customHeight="1">
-      <x:c r="A22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이벤트</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">event_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions, place_id→places</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">content_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">content_id, title, overview, area_code, start_date, end_date, thumbnail_url, fixed_tags, participant_count, source, verify_radius_m, created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EVT-001~023</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">반경 적용 순서: events.verify_radius_m → regions.default_event_verify_radius_m → 2,000m. created_at은 EVT-008 신규 판정 기준</x:t>
-        </x:is>
+      <x:c r="A22" s="37" t="str">
+        <x:v>뱃지</x:v>
+      </x:c>
+      <x:c r="B22" s="37" t="str">
+        <x:v>badges</x:v>
+      </x:c>
+      <x:c r="C22" s="37" t="str">
+        <x:v>badge_id</x:v>
+      </x:c>
+      <x:c r="D22" s="37" t="str">
+        <x:v>event_id→events, area_code→regions</x:v>
+      </x:c>
+      <x:c r="E22" s="37" t="str">
+        <x:v>code, event_id</x:v>
+      </x:c>
+      <x:c r="F22" s="37" t="str">
+        <x:v>type, name_ko, name_en, description, icon_url, condition_json, is_obtainable, available_from, available_to</x:v>
+      </x:c>
+      <x:c r="G22" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H22" s="37" t="str">
+        <x:v>BDG-001~013</x:v>
+      </x:c>
+      <x:c r="I22" s="37" t="str">
+        <x:v>이벤트 연결은 badges.event_id 한 방향</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
-      <x:c r="A23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">뱃지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">badge_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">event_id→events, area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">code, event_id(조건부)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">type, name_ko, name_en, description, icon_url, condition_json, is_obtainable, available_from, available_to</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BDG-001~013</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이벤트 뱃지는 events 1:0..1</x:t>
-        </x:is>
+      <x:c r="A23" s="37" t="str">
+        <x:v>뱃지</x:v>
+      </x:c>
+      <x:c r="B23" s="37" t="str">
+        <x:v>user_badges</x:v>
+      </x:c>
+      <x:c r="C23" s="37" t="str">
+        <x:v>(user_id, badge_id)</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="str">
+        <x:v>user_id→users, badge_id→badges, source_post_id→posts</x:v>
+      </x:c>
+      <x:c r="E23" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F23" s="37" t="str">
+        <x:v>earned_at</x:v>
+      </x:c>
+      <x:c r="G23" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H23" s="37" t="str">
+        <x:v>BDG-005~006, BDG-009~014</x:v>
+      </x:c>
+      <x:c r="I23" s="37" t="str">
+        <x:v>근거 게시글 삭제 시 source_post_id만 NULL</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
-      <x:c r="A24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">뱃지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_badges</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(user_id, badge_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users, badge_id→badges, source_post_id→posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">earned_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BDG-005~006, BDG-009</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">중복 지급 방지</x:t>
-        </x:is>
+      <x:c r="A24" s="37" t="str">
+        <x:v>방문</x:v>
+      </x:c>
+      <x:c r="B24" s="37" t="str">
+        <x:v>visits</x:v>
+      </x:c>
+      <x:c r="C24" s="37" t="str">
+        <x:v>visit_id</x:v>
+      </x:c>
+      <x:c r="D24" s="37" t="str">
+        <x:v>user_id→users, place_id→places, post_id→posts</x:v>
+      </x:c>
+      <x:c r="E24" s="37" t="str">
+        <x:v>(user_id, place_id, visited_on)</x:v>
+      </x:c>
+      <x:c r="F24" s="37" t="str">
+        <x:v>visited_on</x:v>
+      </x:c>
+      <x:c r="G24" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H24" s="37" t="str">
+        <x:v>VST-001~004</x:v>
+      </x:c>
+      <x:c r="I24" s="37" t="str">
+        <x:v>같은 날 같은 장소는 1회</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="33" customFormat="1" ht="97.19999694824219" customHeight="1">
-      <x:c r="A25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">방문</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visit_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">user_id→users, place_id→places, post_id→posts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(user_id, place_id, visited_on)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visited_on</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VST-001~005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">높음·보통만 기록</x:t>
-        </x:is>
+      <x:c r="A25" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="B25" s="37" t="str">
+        <x:v>post_rankings</x:v>
+      </x:c>
+      <x:c r="C25" s="37" t="str">
+        <x:v>(post_id, period)</x:v>
+      </x:c>
+      <x:c r="D25" s="37" t="str">
+        <x:v>post_id→posts.post_id</x:v>
+      </x:c>
+      <x:c r="E25" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F25" s="37" t="str">
+        <x:v>score, rank_no, calculated_at</x:v>
+      </x:c>
+      <x:c r="G25" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="H25" s="37" t="str">
+        <x:v>PST-035, CMU-002, CMU-008~009</x:v>
+      </x:c>
+      <x:c r="I25" s="37" t="str">
+        <x:v>기간별 인기 게시글 사전 집계</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="33" customFormat="1" ht="54" customHeight="1">
-      <x:c r="A26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">heatmap_cells</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cell_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">top_place_id→places; sample_post_ids는 논리 참조</x:t>
-        </x:is>
+      <x:c r="A26" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="B26" s="37" t="str">
+        <x:v>heatmap_cells</x:v>
+      </x:c>
+      <x:c r="C26" s="37" t="str">
+        <x:v>cell_id</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="str">
+        <x:v>top_place_id→places; sample_post_ids는 논리 참조</x:v>
       </x:c>
       <x:c r="E26" s="37" t="str">
-        <x:v>(period, grid_level, lat_index, lng_index)</x:v>
+        <x:v>(grid_level, period, lat, lng)</x:v>
       </x:c>
       <x:c r="F26" s="37" t="str">
-        <x:v>grid_level, lat_index, lng_index, lat, lng, period, post_count, visit_count, user_count, top_place_id, sample_post_ids, sample_thumbnail_urls, last_posted_at, calculated_at</x:v>
-      </x:c>
-      <x:c r="G26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MAP-008~025</x:t>
-        </x:is>
+        <x:v>grid_level, lat, lng, period, post_count, visit_count, user_count, sample_post_ids, last_posted_at, calculated_at</x:v>
+      </x:c>
+      <x:c r="G26" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="H26" s="37" t="str">
+        <x:v>MAP-008~025</x:v>
       </x:c>
       <x:c r="I26" s="37" t="str">
-        <x:v>후보 ID·썸네일 URL 배열은 같은 인덱스로 대응. visit_count는 VST 구현 전까지 0</x:v>
+        <x:v>줌 4단계·기간별 사전 집계. 후보 게시글 최대 10개</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
-      <x:c r="A27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">region_stats</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(area_code, period)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PK 자체</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_count, contributor_count, calculated_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MAP-005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I27" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지역 레이어 버블. period는 heatmap_period 공유 (MAP-005)</x:t>
-        </x:is>
+      <x:c r="A27" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="B27" s="37" t="str">
+        <x:v>region_stats</x:v>
+      </x:c>
+      <x:c r="C27" s="37" t="str">
+        <x:v>(area_code, period)</x:v>
+      </x:c>
+      <x:c r="D27" s="37" t="str">
+        <x:v>area_code→regions</x:v>
+      </x:c>
+      <x:c r="E27" s="37" t="str">
+        <x:v>PK 자체</x:v>
+      </x:c>
+      <x:c r="F27" s="37" t="str">
+        <x:v>post_count, contributor_count</x:v>
+      </x:c>
+      <x:c r="G27" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="H27" s="37" t="str">
+        <x:v>MAP-005</x:v>
+      </x:c>
+      <x:c r="I27" s="37" t="str">
+        <x:v>지역 레이어 버블용</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="33" customFormat="1" ht="97.19999694824219" customHeight="1">
-      <x:c r="A28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_rankings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ranking_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">place_id→places, area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(place_id, period, theme)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code, period, theme, score, rank_no, previous_rank, calculated_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RNK-001~010</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">조회는 이 테이블만 읽는다. 조회 인덱스 (area_code, period, theme, rank_no) (DBML v1.1.3)</x:t>
-        </x:is>
+      <x:c r="A28" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="B28" s="37" t="str">
+        <x:v>place_rankings</x:v>
+      </x:c>
+      <x:c r="C28" s="37" t="str">
+        <x:v>ranking_id</x:v>
+      </x:c>
+      <x:c r="D28" s="37" t="str">
+        <x:v>place_id→places, area_code→regions</x:v>
+      </x:c>
+      <x:c r="E28" s="37" t="str">
+        <x:v>(place_id, period, theme)</x:v>
+      </x:c>
+      <x:c r="F28" s="37" t="str">
+        <x:v>period, theme, score, rank_no, previous_rank, calculated_at</x:v>
+      </x:c>
+      <x:c r="G28" s="37" t="str">
+        <x:v>집계</x:v>
+      </x:c>
+      <x:c r="H28" s="37" t="str">
+        <x:v>RNK-001~010</x:v>
+      </x:c>
+      <x:c r="I28" s="37" t="str">
+        <x:v>지역·기간·테마별 장소 순위 사전 집계</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="33" customFormat="1" ht="97.19999694824219" customHeight="1">
-      <x:c r="A29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_rankings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(post_id, period)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">post_id→posts.post_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(period, rank_no)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">score, rank_no, calculated_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집계</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-035, CMU-002, CMU-008~009</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기간별 인기 게시글은 이 테이블만 읽는다. 조회 시 계산 금지 (JOB-013)</x:t>
-        </x:is>
+      <x:c r="A29" s="37" t="str">
+        <x:v>알림</x:v>
+      </x:c>
+      <x:c r="B29" s="37" t="str">
+        <x:v>notifications</x:v>
+      </x:c>
+      <x:c r="C29" s="37" t="str">
+        <x:v>notification_id</x:v>
+      </x:c>
+      <x:c r="D29" s="37" t="str">
+        <x:v>recipient_id→users, actor_id→users; target는 논리 FK</x:v>
+      </x:c>
+      <x:c r="E29" s="37" t="str">
+        <x:v>(recipient_id, actor_id, type, target_type, target_id)</x:v>
+      </x:c>
+      <x:c r="F29" s="37" t="str">
+        <x:v>type, target_type, target_id, message_key, message_params, is_read, created_at</x:v>
+      </x:c>
+      <x:c r="G29" s="37" t="str">
+        <x:v>물리</x:v>
+      </x:c>
+      <x:c r="H29" s="37" t="str">
+        <x:v>NTF-001~014</x:v>
+      </x:c>
+      <x:c r="I29" s="37" t="str">
+        <x:v>완성 문장 대신 메시지 키와 파라미터 저장</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="33" customFormat="1" ht="97.19999694824219" customHeight="1">
-      <x:c r="A30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">알림</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notifications</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">notification_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">recipient_id→users, actor_id→users; target는 논리 FK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(recipient_id, actor_id, type, target_type, target_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">type, target_type, target_id, message_key, message_params, is_read, created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">물리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NTF-001~014</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">중복 방지는 5컬럼 UNIQUE (DBML v1.1.3)</x:t>
-        </x:is>
+      <x:c r="A30" s="37" t="str">
+        <x:v>운영</x:v>
+      </x:c>
+      <x:c r="B30" s="37" t="str">
+        <x:v>reports</x:v>
+      </x:c>
+      <x:c r="C30" s="37" t="str">
+        <x:v>report_id</x:v>
+      </x:c>
+      <x:c r="D30" s="37" t="str">
+        <x:v>reporter_id→users; target는 논리 FK</x:v>
+      </x:c>
+      <x:c r="E30" s="37" t="str">
+        <x:v>(reporter_id, target_type, target_id)</x:v>
+      </x:c>
+      <x:c r="F30" s="37" t="str">
+        <x:v>reason, status, created_at</x:v>
+      </x:c>
+      <x:c r="G30" s="37" t="str">
+        <x:v>논리</x:v>
+      </x:c>
+      <x:c r="H30" s="37" t="str">
+        <x:v>PST-043~045, PLC-023</x:v>
+      </x:c>
+      <x:c r="I30" s="37" t="str">
+        <x:v>POST/COMMENT/PLACE/USER 다형 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
-      <x:c r="A31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">운영</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reports</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">report_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reporter_id→users; target는 논리 FK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(reporter_id, target_type, target_id)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reason, detail, status, action, reviewed_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">논리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PST-043~045, SYS-017</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">다형 대상. detail·action·reviewed_at은 보강(SYS-017 운영 검토 근거, DBML 미포함)</x:t>
-        </x:is>
+      <x:c r="A31" s="37" t="str">
+        <x:v>운영</x:v>
+      </x:c>
+      <x:c r="B31" s="37" t="str">
+        <x:v>sync_logs</x:v>
+      </x:c>
+      <x:c r="C31" s="37" t="str">
+        <x:v>sync_id</x:v>
+      </x:c>
+      <x:c r="D31" s="37" t="str">
+        <x:v>area_code→regions</x:v>
+      </x:c>
+      <x:c r="E31" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F31" s="37" t="str">
+        <x:v>job_type, content_type_id, result, count, message, created_at</x:v>
+      </x:c>
+      <x:c r="G31" s="37" t="str">
+        <x:v>감사 보존</x:v>
+      </x:c>
+      <x:c r="H31" s="37" t="str">
+        <x:v>PLC-008~009</x:v>
+      </x:c>
+      <x:c r="I31" s="37" t="str">
+        <x:v>조합 단위 동기화 결과 기록</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">운영</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sync_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sync_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">job_type, area_code, content_type_id, result, count, message, created_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">감사 보존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLC-009, SYS-015</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">조합 단위 트랜잭션 분리 결과. result는 SUCCESS/FAIL/PARTIAL</x:t>
-        </x:is>
+      <x:c r="A32" s="37" t="str">
+        <x:v>운영</x:v>
+      </x:c>
+      <x:c r="B32" s="37" t="str">
+        <x:v>search_logs</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="str">
+        <x:v>log_id</x:v>
+      </x:c>
+      <x:c r="D32" s="37" t="str">
+        <x:v>area_code→regions</x:v>
+      </x:c>
+      <x:c r="E32" s="37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F32" s="37" t="str">
+        <x:v>keyword, searched_at</x:v>
+      </x:c>
+      <x:c r="G32" s="37" t="str">
+        <x:v>기간 보존</x:v>
+      </x:c>
+      <x:c r="H32" s="37" t="str">
+        <x:v>SCH-010</x:v>
+      </x:c>
+      <x:c r="I32" s="37" t="str">
+        <x:v>인기 검색어 집계용. user_id 없음</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">운영</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">log_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">area_code→regions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">keyword, area_code, searched_at</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기간 보존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SCH-010~011</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">인기 검색어 집계용. 최근 검색어(SCH-011) 저장소는 미정 — DBML 미결정 10</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A33" s="37"/>
+      <x:c r="B33" s="37"/>
+      <x:c r="C33" s="37"/>
+      <x:c r="D33" s="37"/>
+      <x:c r="E33" s="37"/>
+      <x:c r="F33" s="37"/>
+      <x:c r="G33" s="37"/>
+      <x:c r="H33" s="37"/>
+      <x:c r="I33" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -53600,7 +52114,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17a0a309e1d84d66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f01753ff2354924"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/specs/snaphere-api-spec-v1.1.5.xlsx
+++ b/docs/specs/snaphere-api-spec-v1.1.5.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 개요" sheetId="1" r:id="R12d827777b0e44fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. API 목록" sheetId="2" r:id="R96b920b6f27c4cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 요청 파라미터" sheetId="3" r:id="Rd711201cf950424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 응답 스키마" sheetId="4" r:id="Rf093336020bc45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 공통 규약" sheetId="5" r:id="Re7bbe8a0e5454d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 에러 코드" sheetId="6" r:id="R039f7824e0284737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 배치·비동기" sheetId="7" r:id="R0e2491da54264f9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 요구사항 추적" sheetId="8" r:id="R7a59adfc22c047f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. ERD 엔터티" sheetId="9" r:id="Rca2e6fc396dc499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. ERD 관계" sheetId="10" r:id="R2e2ffc762c1d438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 개요" sheetId="1" r:id="R5884414492c249d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. API 목록" sheetId="2" r:id="R277d73defaba4cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 요청 파라미터" sheetId="3" r:id="R5855b853d5284058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 응답 스키마" sheetId="4" r:id="R6dfb7574134f4606"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 공통 규약" sheetId="5" r:id="Re1400ff3c95d4c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 에러 코드" sheetId="6" r:id="R8f8e03bd7edc480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 배치·비동기" sheetId="7" r:id="R4209a4ace7704e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 요구사항 추적" sheetId="8" r:id="R066a3b605ada4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. ERD 엔터티" sheetId="9" r:id="R72ad145913764f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. ERD 관계" sheetId="10" r:id="Ra8258899434b4058"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -145,7 +145,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -272,6 +272,15 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1870,21 +1879,17 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">D-9</x:t>
         </x:is>
       </x:c>
-      <x:c r="B60" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">남은 미결</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C60" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최근 검색어(SCH-011)·최근 본 장소(VST-006) 저장소는 DBML 미결정 10 — API 비고에 그대로 표기</x:t>
-        </x:is>
+      <x:c r="B60" s="51" t="str">
+        <x:v>검색 저장소</x:v>
+      </x:c>
+      <x:c r="C60" s="51" t="str">
+        <x:v>최근 검색어(SCH-011)는 Redis에 사용자별 최대 20개·TTL 30일로 저장. 최근 본 장소(VST-006)는 별도 결정 유지</x:v>
       </x:c>
       <x:c r="D60" s="40" t="inlineStr">
         <x:is>
@@ -3184,7 +3189,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc654fc8c17bf45a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a346d53762144f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9868,7 +9873,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="85" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
+    <x:row r="85" s="33" customFormat="1" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A85" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-001</x:t>
@@ -9904,53 +9909,49 @@
           <x:t xml:space="preserve">Must</x:t>
         </x:is>
       </x:c>
-      <x:c r="H85" s="37" t="inlineStr">
+      <x:c r="H85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">장소·게시글·사용자·태그를 통합 검색하고 타입별 상위를 반환한다.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I85" s="37" t="inlineStr">
+      <x:c r="I85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="J85" s="37" t="inlineStr">
+      <x:c r="J85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SearchResult</x:t>
         </x:is>
       </x:c>
-      <x:c r="K85" s="37" t="inlineStr">
+      <x:c r="K85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">200</x:t>
         </x:is>
       </x:c>
-      <x:c r="L85" s="37" t="inlineStr">
+      <x:c r="L85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">COMMON_400, AUTH_REQUIRED, COMMON_500</x:t>
         </x:is>
       </x:c>
-      <x:c r="M85" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">타입별 cursor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N85" s="37" t="inlineStr">
+      <x:c r="M85" s="52" t="str">
+        <x:v>단일 types 지정 시 불투명 keyset cursor</x:v>
+      </x:c>
+      <x:c r="N85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="O85" s="37" t="inlineStr">
+      <x:c r="O85" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-001, SCH-003~009</x:t>
         </x:is>
       </x:c>
-      <x:c r="P85" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">places, posts, users, tags, search_logs</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="86" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
+      <x:c r="P85" s="52" t="str">
+        <x:v>places, posts, users, tags, search_logs(커서 없는 첫 페이지 검색만 기록)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-002</x:t>
@@ -9986,53 +9987,49 @@
           <x:t xml:space="preserve">Could</x:t>
         </x:is>
       </x:c>
-      <x:c r="H86" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">검색 로그 집계 기반 인기 검색어를 반환한다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I86" s="37" t="inlineStr">
+      <x:c r="H86" s="52" t="str">
+        <x:v>최근 7일 검색 로그 집계 기반 인기 검색어를 반환한다.</x:v>
+      </x:c>
+      <x:c r="I86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="J86" s="37" t="inlineStr">
+      <x:c r="J86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PopularKeyword[]</x:t>
         </x:is>
       </x:c>
-      <x:c r="K86" s="37" t="inlineStr">
+      <x:c r="K86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">200</x:t>
         </x:is>
       </x:c>
-      <x:c r="L86" s="37" t="inlineStr">
+      <x:c r="L86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">COMMON_400, AUTH_REQUIRED, COMMON_500</x:t>
         </x:is>
       </x:c>
-      <x:c r="M86" s="37" t="inlineStr">
+      <x:c r="M86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="N86" s="37" t="inlineStr">
+      <x:c r="N86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">10m</x:t>
         </x:is>
       </x:c>
-      <x:c r="O86" s="37" t="inlineStr">
+      <x:c r="O86" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-002, SCH-010</x:t>
         </x:is>
       </x:c>
-      <x:c r="P86" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="87" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
+      <x:c r="P86" s="52" t="str">
+        <x:v>search_logs(30일 보존), Redis(10분 캐시)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-003</x:t>
@@ -10068,53 +10065,51 @@
           <x:t xml:space="preserve">Could</x:t>
         </x:is>
       </x:c>
-      <x:c r="H87" s="37" t="inlineStr">
+      <x:c r="H87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">사용자의 최근 검색어를 조회한다.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I87" s="37" t="inlineStr">
+      <x:c r="I87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="J87" s="37" t="inlineStr">
+      <x:c r="J87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RecentSearch[]</x:t>
         </x:is>
       </x:c>
-      <x:c r="K87" s="37" t="inlineStr">
+      <x:c r="K87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">200</x:t>
         </x:is>
       </x:c>
-      <x:c r="L87" s="37" t="inlineStr">
+      <x:c r="L87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">COMMON_400, AUTH_REQUIRED, COMMON_500</x:t>
         </x:is>
       </x:c>
-      <x:c r="M87" s="37" t="inlineStr">
+      <x:c r="M87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="N87" s="37" t="inlineStr">
+      <x:c r="N87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="O87" s="37" t="inlineStr">
+      <x:c r="O87" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-002, SCH-011</x:t>
         </x:is>
       </x:c>
-      <x:c r="P87" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs / ※ 최근 검색어 저장소 미정 — 앱 로컬·Redis·별도 테이블 (DBML 미결정 10)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="88" s="33" customFormat="1" ht="118.80000305175781" customHeight="1">
+      <x:c r="P87" s="52" t="str">
+        <x:v>Redis(사용자별 최대 20개, TTL 30일, 동일 검색어 최신화)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-004</x:t>
@@ -10150,50 +10145,48 @@
           <x:t xml:space="preserve">Could</x:t>
         </x:is>
       </x:c>
-      <x:c r="H88" s="37" t="inlineStr">
+      <x:c r="H88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">최근 검색어 한 건 또는 전체를 삭제한다.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I88" s="37" t="inlineStr">
+      <x:c r="I88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="J88" s="37" t="inlineStr">
+      <x:c r="J88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empty</x:t>
         </x:is>
       </x:c>
-      <x:c r="K88" s="37" t="inlineStr">
+      <x:c r="K88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">204</x:t>
         </x:is>
       </x:c>
-      <x:c r="L88" s="37" t="inlineStr">
+      <x:c r="L88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">COMMON_400, AUTH_REQUIRED, COMMON_500</x:t>
         </x:is>
       </x:c>
-      <x:c r="M88" s="37" t="inlineStr">
+      <x:c r="M88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="N88" s="37" t="inlineStr">
+      <x:c r="N88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="O88" s="37" t="inlineStr">
+      <x:c r="O88" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-011</x:t>
         </x:is>
       </x:c>
-      <x:c r="P88" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
+      <x:c r="P88" s="52" t="str">
+        <x:v>Redis(검색어 1건 또는 전체 삭제)</x:v>
       </x:c>
     </x:row>
     <x:row r="89" s="33" customFormat="1" ht="64.80000305175781" customHeight="1">
@@ -11283,7 +11276,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67f956d6004945ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc40bba46128a4a00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21198,7 +21191,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="198" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
+    <x:row r="198" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-001</x:t>
@@ -21234,10 +21227,8 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H198" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLACE|POST|USER|TAG</x:t>
-        </x:is>
+      <x:c r="H198" s="52" t="str">
+        <x:v>PLACE|POST|USER|TAG, cursor 사용 시 정확히 1개</x:v>
       </x:c>
       <x:c r="I198" s="37" t="inlineStr">
         <x:is>
@@ -21250,7 +21241,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="199" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="199" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-001</x:t>
@@ -21286,10 +21277,8 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H199" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">필터</x:t>
-        </x:is>
+      <x:c r="H199" s="52" t="str">
+        <x:v>지역명과 정확히 일치하면 해당 지역 코드가 우선</x:v>
       </x:c>
       <x:c r="I199" s="37" t="inlineStr">
         <x:is>
@@ -21302,7 +21291,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="200" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="200" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-001</x:t>
@@ -21338,10 +21327,8 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H200" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">더보기 타입의 커서</x:t>
-        </x:is>
+      <x:c r="H200" s="52" t="str">
+        <x:v>단일 검색 타입용 불투명 keyset cursor</x:v>
       </x:c>
       <x:c r="I200" s="37" t="inlineStr">
         <x:is>
@@ -21354,7 +21341,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="201" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="201" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-001</x:t>
@@ -21390,7 +21377,7 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H201" s="37" t="inlineStr">
+      <x:c r="H201" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">타입별 기본 5, 더보기 최대 50</x:t>
         </x:is>
@@ -21404,7 +21391,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="202" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="202" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-002</x:t>
@@ -21440,7 +21427,7 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H202" s="37" t="inlineStr">
+      <x:c r="H202" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
@@ -21456,7 +21443,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="203" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="203" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">API-SCH-002</x:t>
@@ -21492,10 +21479,8 @@
           <x:t xml:space="preserve">N</x:t>
         </x:is>
       </x:c>
-      <x:c r="H203" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기본 10</x:t>
-        </x:is>
+      <x:c r="H203" s="52" t="str">
+        <x:v>기본 10, 최대 50</x:v>
       </x:c>
       <x:c r="I203" s="37" t="n">
         <x:v>10</x:v>
@@ -23374,7 +23359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ec598875e54713"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43dc20b6cebc4012"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33995,7 +33980,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="297" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
+    <x:row r="297" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A297" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RecentSearch</x:t>
@@ -34021,18 +34006,14 @@
           <x:t xml:space="preserve">검색 로그 ID</x:t>
         </x:is>
       </x:c>
-      <x:c r="F297" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sch_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G297" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="298" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
+      <x:c r="F297" s="52" t="str">
+        <x:v>550e8400-e29b-41d4-a716-446655440000</x:v>
+      </x:c>
+      <x:c r="G297" s="52" t="str">
+        <x:v>Redis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A298" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RecentSearch</x:t>
@@ -34058,18 +34039,16 @@
           <x:t xml:space="preserve">검색어</x:t>
         </x:is>
       </x:c>
-      <x:c r="F298" s="37" t="inlineStr">
+      <x:c r="F298" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">경복궁</x:t>
         </x:is>
       </x:c>
-      <x:c r="G298" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="299" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
+      <x:c r="G298" s="52" t="str">
+        <x:v>Redis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A299" s="45" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RecentSearch</x:t>
@@ -34095,15 +34074,13 @@
           <x:t xml:space="preserve">검색 시각</x:t>
         </x:is>
       </x:c>
-      <x:c r="F299" s="46" t="inlineStr">
+      <x:c r="F299" s="53" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">예: 2026-09-01T09:00:00+09:00</x:t>
         </x:is>
       </x:c>
-      <x:c r="G299" s="46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">search_logs</x:t>
-        </x:is>
+      <x:c r="G299" s="53" t="str">
+        <x:v>Redis</x:v>
       </x:c>
     </x:row>
     <x:row r="300" s="33" customFormat="1" ht="21.600000381469727" customHeight="1">
@@ -35259,7 +35236,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb159703a09a24102"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb480bbbd2ff4f38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35915,7 +35892,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf4037cd02f74f3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9bb24f5de324496"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37621,7 +37598,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e4e96357354eef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1b80956fc6d4a40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38249,7 +38226,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba54ab3ab10e45c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e2f3f81516b47bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50162,7 +50139,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="273" s="33" customFormat="1" ht="32.400001525878906" customHeight="1">
+    <x:row r="273" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A273" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-010</x:t>
@@ -50199,13 +50176,11 @@
         </x:is>
       </x:c>
       <x:c r="H273" s="37" t="str"/>
-      <x:c r="I273" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔드포인트 계약에 직접 반영</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="274" s="33" customFormat="1" ht="43.20000076293945" customHeight="1">
+      <x:c r="I273" s="52" t="str">
+        <x:v>최근 7일 검색 로그 집계, Redis 10분 캐시, 로그 30일 보존</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" s="33" customFormat="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A274" s="37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SCH-011</x:t>
@@ -50242,10 +50217,8 @@
         </x:is>
       </x:c>
       <x:c r="H274" s="37" t="str"/>
-      <x:c r="I274" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">엔드포인트 계약에 직접 반영</x:t>
-        </x:is>
+      <x:c r="I274" s="52" t="str">
+        <x:v>Redis 사용자별 최대 20개, TTL 30일; 동일 검색어는 최신 순서로 갱신</x:v>
       </x:c>
     </x:row>
     <x:row r="275" s="33" customFormat="1" ht="54" customHeight="1">
@@ -51221,7 +51194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646cc4da6ffe4c8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf7e94829a64c34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52067,7 +52040,7 @@
         <x:v>조합 단위 동기화 결과 기록</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="37" t="str">
         <x:v>운영</x:v>
       </x:c>
@@ -52092,8 +52065,8 @@
       <x:c r="H32" s="37" t="str">
         <x:v>SCH-010</x:v>
       </x:c>
-      <x:c r="I32" s="37" t="str">
-        <x:v>인기 검색어 집계용. user_id 없음</x:v>
+      <x:c r="I32" s="52" t="str">
+        <x:v>인기 검색어 집계용. user_id 없음. 최근 7일 집계·30일 보존</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -52114,7 +52087,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f01753ff2354924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R883619f92ba443bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>